--- a/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,62</t>
+          <t>1,82; 15,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,26</t>
+          <t>1,05; 9,93</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,99</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,9</t>
+          <t>0,52; 5,15</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 7,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,01</t>
+          <t>0,0; 9,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,3</t>
+          <t>0,0; 14,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,42</t>
+          <t>1,13; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,59</t>
+          <t>0,47; 3,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,69</t>
+          <t>0,51; 2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,65</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>582; 4923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3586</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>637; 6036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3375</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4453</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4083</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4474</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3106</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>533; 5313</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3340</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3324</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3062</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3421</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4326</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3600</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3463</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4855</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3248</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4994</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1836; 8510</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>673; 5186</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>605; 5577</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1371; 8042</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>628; 6243</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2576; 10070</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,35</t>
+          <t>1,85; 16,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,93</t>
+          <t>1,06; 10,04</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,15</t>
+          <t>0,51; 5,67</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,94</t>
+          <t>0,0; 16,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,2</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,24</t>
+          <t>0,92; 4,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,6</t>
+          <t>0,47; 4,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,31; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,99</t>
+          <t>0,51; 3,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,83; 3,4</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>582; 4923</t>
+          <t>593; 5336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 3114</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>637; 6036</t>
+          <t>645; 6100</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3375</t>
+          <t>0; 3318</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,37 +1590,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4453</t>
+          <t>0; 4579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 3186</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4083</t>
+          <t>0; 3611</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4474</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3312</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>533; 5313</t>
+          <t>531; 5849</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3340</t>
+          <t>0; 3110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>0; 3542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3062</t>
+          <t>0; 3039</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3421</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4326</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4396</t>
+          <t>0; 3787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 3694</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3463</t>
+          <t>0; 3920</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4855</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3248</t>
+          <t>0; 3277</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 3813</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1836; 8510</t>
+          <t>1497; 8050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>673; 5186</t>
+          <t>672; 6954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>605; 5577</t>
+          <t>602; 5531</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1371; 8042</t>
+          <t>1373; 8220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>628; 6243</t>
+          <t>629; 5706</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2576; 10070</t>
+          <t>2575; 10557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>6,08%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,64</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>1,87; 16,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,04</t>
+          <t>1,07; 10,26</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,67</t>
+          <t>0,52; 4,9</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 16,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,47; 4,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,95</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,83</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,89</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,9; 5,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,05</t>
+          <t>0,51; 2,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,16; 1,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,4</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1321,22 +1321,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>1950</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>593; 5336</t>
+          <t>0; 3779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3114</t>
+          <t>599; 5330</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>645; 6100</t>
+          <t>650; 6237</t>
         </is>
       </c>
     </row>
@@ -1479,27 +1479,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1306</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3318</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4579</t>
+          <t>0; 4020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3491</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3186</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 4491</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4286</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3312</t>
+          <t>0; 2716</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>531; 5849</t>
+          <t>534; 5059</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,27 +1690,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3542</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3039</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>0; 3409</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>767</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>0; 4081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3933</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5054</t>
+          <t>0; 5501</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3277</t>
+          <t>0; 3679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3813</t>
+          <t>0; 3859</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4028</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>670; 6599</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>608; 5694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1497; 8050</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>672; 6954</t>
+          <t>0; 5206</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>602; 5531</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>1461; 8802</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1373; 8220</t>
+          <t>1366; 7249</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>629; 5706</t>
+          <t>624; 6247</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2575; 10557</t>
+          <t>2439; 9734</t>
         </is>
       </c>
     </row>
